--- a/PIT_Reform_Optimization_Engine_2/PIT_slabs_2025.xlsx
+++ b/PIT_Reform_Optimization_Engine_2/PIT_slabs_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8b528d25ed835976/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Pakistan_Income_Tax_Slabs_app\PIT_Reform_Optimization_Engine_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{841CA8BD-F63D-4B70-8970-4C9AE0222259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6302DD57-9CD0-44F6-A68D-B6A23C2D8392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{B6C5576D-69C9-41B7-A1DE-B19EF1B3A571}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="27">
   <si>
     <t>MTR</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Surcharge</t>
   </si>
   <si>
-    <t>of the tax liability</t>
-  </si>
-  <si>
     <t>Tax_Type</t>
   </si>
   <si>
@@ -105,6 +102,21 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>Rs. 6,000 + 11% of the amount exceeding Rs. 1,200,000</t>
+  </si>
+  <si>
+    <t>Rs. 116,000 + 23% of the amount exceeding Rs. 2,200,000</t>
+  </si>
+  <si>
+    <t>Rs. 345,000 + 30% of the amount exceeding Rs. 3,200,000</t>
+  </si>
+  <si>
+    <t>Rs. 616,000 + 35% of the amount exceeding Rs. 4,100,000</t>
   </si>
 </sst>
 </file>
@@ -128,12 +140,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -165,7 +183,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -178,7 +195,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -515,445 +535,1134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059270FF-07F6-47F8-8995-82961C9214B7}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.86328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2200001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4100000</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4100000</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5600000</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5600001</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3200001</v>
+      </c>
+      <c r="D20" s="5">
+        <v>5600000</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5">
+        <v>5600001</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5600000</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5600001</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C30" s="1">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2200001</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D34" s="1">
+        <v>4100000</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1">
+        <v>4100000</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C39" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D41" s="1">
+        <v>5600000</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="1">
+        <v>5600001</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0</v>
+      </c>
+      <c r="D44" s="1">
         <v>600000</v>
       </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1">
         <v>600001</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D45" s="1">
         <v>1200000</v>
       </c>
-      <c r="E3" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="E45" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1">
         <v>1200001</v>
       </c>
-      <c r="D4" s="2">
-        <v>2200000</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D46" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3200000</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3200001</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5600000</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
+        <v>5600001</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="1">
+        <v>600001</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1200000</v>
+      </c>
+      <c r="E52" s="1">
         <v>0.15</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2200001</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="F52" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1200001</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1600000</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1600001</v>
+      </c>
+      <c r="D54" s="1">
         <v>3200000</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="E54" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="1">
         <v>3200001</v>
       </c>
-      <c r="D6" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>4100000</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="D55" s="1">
+        <v>5600000</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="1">
+        <v>5600001</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="E56" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D57" s="1"/>
+      <c r="E57" s="1">
         <v>0.1</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>600000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2">
-        <v>600001</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1200000</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1200001</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1600000</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1600001</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3200001</v>
-      </c>
-      <c r="D14" s="2">
-        <v>5600000</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2">
-        <v>5600001</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="F57" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>600000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2">
-        <v>600001</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1200000</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1200001</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1600000</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1600001</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3200000</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3200001</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
